--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -19128,16 +19128,16 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2883</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -23689,12 +23689,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -23728,16 +23728,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -23770,42 +23770,338 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW143" t="inlineStr">
+      <c r="AW144" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY143" t="inlineStr">
+      <c r="AY144" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA143" t="inlineStr">
+      <c r="BA144" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB143" t="inlineStr">
+      <c r="BB144" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC143" t="inlineStr">
+      <c r="BC144" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23842,7 +24138,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -23925,7 +24221,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -23935,7 +24231,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -23987,7 +24283,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -1505,9 +1499,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2150,7 +2141,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2297,9 +2288,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -4469,9 +4457,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4617,9 +4602,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -4765,9 +4747,6 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -5410,7 +5389,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -5557,9 +5536,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -7581,9 +7557,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7729,9 +7702,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7877,9 +7847,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -8522,7 +8489,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -8669,9 +8636,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -10397,9 +10361,6 @@
       <c r="O61" t="n">
         <v>10</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.0367281181951979</v>
       </c>
@@ -10693,9 +10654,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10841,9 +10799,6 @@
       <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -10989,9 +10944,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -11385,9 +11337,6 @@
       <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1513008373177463</v>
       </c>
@@ -11634,7 +11583,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -11781,9 +11730,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12177,9 +12123,6 @@
       <c r="O71" t="n">
         <v>3</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -13509,9 +13452,6 @@
       <c r="O80" t="n">
         <v>9</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.03305530637567811</v>
       </c>
@@ -13657,9 +13597,6 @@
       <c r="O81" t="n">
         <v>1662</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.7782259077571501</v>
       </c>
@@ -13953,9 +13890,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14101,9 +14035,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -14249,9 +14180,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14645,9 +14573,6 @@
       <c r="O87" t="n">
         <v>9</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.1702134419824646</v>
       </c>
@@ -14894,7 +14819,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -15041,9 +14966,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15437,9 +15359,6 @@
       <c r="O91" t="n">
         <v>5</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -17065,9 +16984,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01836405909759895</v>
       </c>
@@ -17213,9 +17129,6 @@
       <c r="O103" t="n">
         <v>731</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.3422882903552808</v>
       </c>
@@ -17509,9 +17422,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -17657,9 +17567,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -17805,9 +17712,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -18201,9 +18105,6 @@
       <c r="O109" t="n">
         <v>15</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.2836890699707744</v>
       </c>
@@ -18450,7 +18351,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -18597,9 +18498,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18993,9 +18891,6 @@
       <c r="O113" t="n">
         <v>10</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.04345692446436896</v>
       </c>
@@ -19141,9 +19036,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -19289,9 +19181,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -19437,9 +19326,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -19585,9 +19471,6 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19733,9 +19616,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -19881,9 +19761,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20029,9 +19906,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20177,9 +20051,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -20325,9 +20196,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -20473,9 +20341,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.0009364932704658844</v>
       </c>
@@ -20621,9 +20486,6 @@
       <c r="O124" t="n">
         <v>2</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -20769,9 +20631,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21165,9 +21024,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -21561,9 +21417,6 @@
       <c r="O129" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -21709,9 +21562,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -21857,9 +21707,6 @@
       <c r="O131" t="n">
         <v>2</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22005,9 +21852,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -22153,9 +21997,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -22301,9 +22142,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -22449,9 +22287,6 @@
       <c r="O135" t="n">
         <v>2</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22597,9 +22432,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -22745,9 +22577,6 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -22893,9 +22722,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23041,9 +22867,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -23184,16 +23007,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R140" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23337,9 +23157,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -23733,9 +23550,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -23881,9 +23695,6 @@
       <c r="O144" t="n">
         <v>3</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -24029,9 +23840,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -24102,6 +23910,151 @@
       <c r="BC145" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24174,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -24231,7 +24184,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -24283,7 +24236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2885</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -21412,13 +21412,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R129" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2887</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -24058,6 +24058,151 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24091,7 +24236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -24184,7 +24329,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -24236,7 +24381,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2888</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -20442,12 +20442,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20481,13 +20481,16 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007077571156938747</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20520,42 +20523,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20587,12 +20590,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20626,95 +20629,81 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20741,7 +20730,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -20790,98 +20779,23 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -20975,17 +20889,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21019,22 +20933,39 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -21042,6 +20973,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21059,7 +21048,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -21072,42 +21061,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21134,7 +21123,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21183,98 +21172,23 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Leptospirainfektion</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -21368,17 +21282,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21412,81 +21326,170 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>3</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.01303707733931069</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21518,12 +21521,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21548,7 +21551,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -21557,13 +21560,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -21596,42 +21599,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21663,12 +21666,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21702,13 +21705,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21741,42 +21744,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21808,12 +21811,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21838,7 +21841,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -21847,13 +21850,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21886,42 +21889,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21953,12 +21956,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21992,13 +21995,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22031,42 +22034,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22098,12 +22101,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22128,7 +22131,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22137,13 +22140,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22176,42 +22179,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22243,12 +22246,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22282,13 +22285,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22321,42 +22324,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22388,12 +22391,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22418,7 +22421,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -22427,13 +22430,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -22466,42 +22469,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22533,12 +22536,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22572,13 +22575,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -22611,42 +22614,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22678,12 +22681,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -22708,7 +22711,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -22717,13 +22720,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -22756,42 +22759,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22823,12 +22826,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22853,12 +22856,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N139" t="n">
@@ -22901,42 +22904,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22968,12 +22971,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23007,13 +23010,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23046,42 +23049,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23113,12 +23116,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23152,95 +23155,81 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23267,7 +23256,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -23316,98 +23305,23 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -23501,17 +23415,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -23545,81 +23459,170 @@
         </is>
       </c>
       <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
         <v>1</v>
       </c>
-      <c r="O143" t="n">
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
         <v>1</v>
       </c>
-      <c r="R143" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
-      <c r="AT143" t="n">
-        <v>0</v>
-      </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23654,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -23690,13 +23693,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -23729,42 +23732,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23796,12 +23799,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -23826,7 +23829,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -23835,13 +23838,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -23874,42 +23877,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23941,12 +23944,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -23971,7 +23974,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -23980,13 +23983,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24019,42 +24022,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24086,12 +24089,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24116,7 +24119,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24131,7 +24134,7 @@
         <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24164,40 +24167,185 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW147" t="inlineStr">
+      <c r="AW148" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX147" t="inlineStr">
+      <c r="AX148" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY147" t="inlineStr">
+      <c r="AY148" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ147" t="inlineStr">
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA147" t="inlineStr">
+      <c r="BA148" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB147" t="inlineStr">
+      <c r="BB148" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC147" t="inlineStr">
+      <c r="BC148" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24319,7 +24467,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -24329,7 +24477,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -24381,7 +24529,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2889</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -24351,6 +24351,151 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24384,7 +24529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -24467,7 +24612,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -24477,7 +24622,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -24529,7 +24674,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2989</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O109" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R109" t="n">
-        <v>0.2836890699707744</v>
+        <v>0.2269512559766195</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -18259,10 +18259,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -21128,12 +21128,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21167,13 +21167,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R128" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -21220,42 +21220,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21287,12 +21287,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21326,29 +21326,29 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Leptospirainfektion</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -21408,17 +21408,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -21454,42 +21454,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21560,81 +21560,95 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21661,17 +21675,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21696,7 +21710,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -21705,81 +21719,170 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21811,12 +21914,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21841,7 +21944,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -21850,13 +21953,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21889,42 +21992,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21986,7 +22089,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22131,7 +22234,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22140,13 +22243,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R134" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22276,7 +22379,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -22421,7 +22524,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -22430,13 +22533,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -22566,7 +22669,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -22711,7 +22814,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -22720,13 +22823,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -22856,7 +22959,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -22971,12 +23074,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23001,22 +23104,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23049,42 +23152,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23116,12 +23219,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23146,22 +23249,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23194,42 +23297,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23364,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23313,82 +23416,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23415,17 +23504,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -23459,170 +23548,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23654,12 +23654,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -23693,81 +23693,95 @@
         </is>
       </c>
       <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
         <v>1</v>
       </c>
-      <c r="O144" t="n">
-        <v>1</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
-      <c r="AT144" t="n">
-        <v>0</v>
-      </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23794,17 +23808,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -23838,81 +23852,170 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>3</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23944,12 +24047,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -23974,7 +24077,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -23983,13 +24086,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24022,42 +24125,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24119,7 +24222,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24128,13 +24231,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24264,7 +24367,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24273,13 +24376,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -24409,7 +24512,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -24493,6 +24596,441 @@
       <c r="BC149" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24529,7 +25067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -24612,7 +25150,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -24622,7 +25160,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -24642,7 +25180,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -24674,7 +25212,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2990</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -30834,12 +30834,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30873,13 +30873,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30912,42 +30912,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30979,12 +30979,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -31018,95 +31018,81 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31133,7 +31119,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -31182,98 +31168,23 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -31367,17 +31278,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31411,22 +31322,39 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>10</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.1891260466471829</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -31434,6 +31362,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -31451,7 +31437,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+          <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -31464,42 +31450,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31526,7 +31512,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -31575,98 +31561,23 @@
       <c r="O181" t="n">
         <v>10</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.1891260466471829</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -31760,17 +31671,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -31804,22 +31715,39 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O182" t="n">
-        <v>2</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -31827,6 +31755,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly leptospirosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -31844,7 +31830,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+          <t>SER_NZ_LEPTOSPIROSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -31857,42 +31843,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31919,7 +31905,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -31968,98 +31954,23 @@
       <c r="O183" t="n">
         <v>2</v>
       </c>
+      <c r="R183" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Leptospirainfektion</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -32153,17 +32064,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32197,81 +32108,170 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O184" t="n">
-        <v>3</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.01303707733931069</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Leptospirainfektion</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32303,12 +32303,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -32342,13 +32342,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -32381,42 +32381,42 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32448,12 +32448,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32487,13 +32487,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -32526,42 +32526,42 @@
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32593,12 +32593,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -32623,7 +32623,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -32637,88 +32637,76 @@
       <c r="O187" t="n">
         <v>2</v>
       </c>
-      <c r="P187" t="n">
-        <v>2</v>
-      </c>
       <c r="R187" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32745,7 +32733,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -32797,98 +32785,18 @@
       <c r="P188" t="n">
         <v>2</v>
       </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R188" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -32982,17 +32890,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33017,7 +32925,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33026,81 +32934,173 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P189" t="n">
+        <v>2</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33132,12 +33132,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33171,13 +33171,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -33210,42 +33210,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33277,12 +33277,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33307,7 +33307,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33321,88 +33321,76 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="P191" t="n">
-        <v>1</v>
-      </c>
       <c r="R191" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33417,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -33481,98 +33469,18 @@
       <c r="P192" t="n">
         <v>1</v>
       </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R192" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -33666,17 +33574,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -33701,7 +33609,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -33710,81 +33618,173 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33816,12 +33816,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -33855,13 +33855,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -33894,42 +33894,42 @@
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33961,12 +33961,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34000,93 +34000,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" t="n">
-        <v>1</v>
-      </c>
-      <c r="P195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R195" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34101,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -34165,98 +34153,18 @@
       <c r="P196" t="n">
         <v>1</v>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R196" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -34350,17 +34258,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34385,7 +34293,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34394,81 +34302,173 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P197" t="n">
+        <v>1</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34500,12 +34500,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -34578,42 +34578,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34645,12 +34645,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -34675,7 +34675,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -34684,13 +34684,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -34723,42 +34723,42 @@
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34790,12 +34790,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -34834,9 +34834,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -34845,77 +34842,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34930,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -34994,98 +34982,18 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -35179,17 +35087,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35214,12 +35122,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N202" t="n">
@@ -35228,76 +35136,168 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35329,12 +35329,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35368,13 +35368,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -35407,42 +35407,42 @@
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35474,12 +35474,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -35513,95 +35513,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35628,7 +35614,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -35677,98 +35663,23 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_605_MONTHLY</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_605_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Leptospirose</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -35862,17 +35773,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -35906,81 +35817,170 @@
         </is>
       </c>
       <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Leptospirose</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
         <v>1</v>
       </c>
-      <c r="O206" t="n">
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_605_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
         <v>1</v>
       </c>
-      <c r="R206" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
-      <c r="AT206" t="n">
-        <v>0</v>
-      </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36012,12 +36012,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36051,13 +36051,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -36090,42 +36090,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36157,12 +36157,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36187,7 +36187,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36196,13 +36196,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -36235,42 +36235,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36302,12 +36302,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36341,93 +36341,81 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>1</v>
-      </c>
-      <c r="P209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36454,7 +36442,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -36506,98 +36494,18 @@
       <c r="P210" t="n">
         <v>1</v>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R210" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -36691,17 +36599,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -36726,7 +36634,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -36740,76 +36648,168 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="R211" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P211" t="n">
+        <v>1</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36841,12 +36841,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -36886,7 +36886,7 @@
         <v>1</v>
       </c>
       <c r="R212" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -36919,42 +36919,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36986,12 +36986,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37025,93 +37025,81 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37138,7 +37126,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -37190,98 +37178,18 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -37375,17 +37283,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -37410,7 +37318,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -37419,81 +37327,173 @@
         </is>
       </c>
       <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
         <v>1</v>
       </c>
-      <c r="O215" t="n">
-        <v>1</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37525,12 +37525,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -37555,7 +37555,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -37564,13 +37564,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -37603,42 +37603,42 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37670,12 +37670,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -37709,93 +37709,81 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
-      </c>
-      <c r="P217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37822,7 +37810,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -37874,98 +37862,18 @@
       <c r="P218" t="n">
         <v>1</v>
       </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>Leptospirosis</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R218" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN218" t="b">
-        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -38031,6 +37939,243 @@
         </is>
       </c>
       <c r="BC218" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>leptospirosis</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="P219" t="n">
+        <v>1</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEPTOSPIROSIS; SER_SG_HIST_LEPTOSPIROSIS</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -38152,7 +38297,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -38162,7 +38307,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d035/2026-2029.xlsx
+++ b/diseases/d035/2026-2029.xlsx
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2321,17 +2321,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2547,7 +2552,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2555,17 +2560,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -7137,7 +7147,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7145,17 +7155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7371,7 +7386,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -7379,17 +7394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11813,7 +11833,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -11821,17 +11841,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -12047,7 +12072,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -12055,17 +12080,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -16877,7 +16907,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -16885,17 +16915,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -17111,7 +17146,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -17119,17 +17154,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -21689,7 +21729,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -21697,17 +21737,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -21923,7 +21968,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -21931,17 +21976,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -27191,7 +27241,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -27199,17 +27249,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -27425,7 +27480,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -27433,17 +27488,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -31979,7 +32039,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
@@ -31987,17 +32047,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS183" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -32213,7 +32278,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
@@ -32221,17 +32286,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS184" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEPTOSPIROSIS</t>
         </is>
       </c>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
